--- a/LMAT_Model.xlsx
+++ b/LMAT_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB656E6-2E6B-4B26-AF33-892DD6704FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6158A5ED-61DF-4F67-8551-8730E3F69365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/LMAT_Model.xlsx
+++ b/LMAT_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6158A5ED-61DF-4F67-8551-8730E3F69365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A63BAF-A340-46FE-8711-585C8644462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,8 @@
   <externalReferences>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -12782,6 +12784,975 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Notes | Quant Analysis"/>
+      <sheetName val="M&amp;A"/>
+      <sheetName val="Management"/>
+      <sheetName val="Markets | Product Lines"/>
+      <sheetName val="NARI"/>
+      <sheetName val="Debt Schedule"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="C5">
+            <v>367.54</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="AW4">
+            <v>467</v>
+          </cell>
+          <cell r="AX4">
+            <v>555</v>
+          </cell>
+          <cell r="AY4">
+            <v>469</v>
+          </cell>
+          <cell r="AZ4">
+            <v>517</v>
+          </cell>
+          <cell r="BA4">
+            <v>525</v>
+          </cell>
+          <cell r="BB4">
+            <v>600</v>
+          </cell>
+          <cell r="BC4">
+            <v>528</v>
+          </cell>
+          <cell r="BD4">
+            <v>563</v>
+          </cell>
+          <cell r="BE4">
+            <v>535</v>
+          </cell>
+          <cell r="BF4">
+            <v>653</v>
+          </cell>
+          <cell r="BG4">
+            <v>566</v>
+          </cell>
+          <cell r="BH4">
+            <v>622</v>
+          </cell>
+          <cell r="BI4">
+            <v>620</v>
+          </cell>
+          <cell r="BJ4">
+            <v>726</v>
+          </cell>
+          <cell r="BK4">
+            <v>667</v>
+          </cell>
+          <cell r="BL4">
+            <v>698</v>
+          </cell>
+          <cell r="BM4">
+            <v>679</v>
+          </cell>
+          <cell r="BN4">
+            <v>790</v>
+          </cell>
+          <cell r="BO4">
+            <v>730</v>
+          </cell>
+          <cell r="BP4">
+            <v>768</v>
+          </cell>
+          <cell r="BQ4">
+            <v>760</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AW5">
+            <v>467</v>
+          </cell>
+          <cell r="AX5">
+            <v>525</v>
+          </cell>
+          <cell r="AY5">
+            <v>469</v>
+          </cell>
+          <cell r="AZ5">
+            <v>518</v>
+          </cell>
+          <cell r="BA5">
+            <v>525</v>
+          </cell>
+          <cell r="BB5">
+            <v>629</v>
+          </cell>
+          <cell r="BC5">
+            <v>538</v>
+          </cell>
+          <cell r="BD5">
+            <v>600</v>
+          </cell>
+          <cell r="BE5">
+            <v>590</v>
+          </cell>
+          <cell r="BF5">
+            <v>997</v>
+          </cell>
+          <cell r="BG5">
+            <v>707</v>
+          </cell>
+          <cell r="BH5">
+            <v>713</v>
+          </cell>
+          <cell r="BI5">
+            <v>746</v>
+          </cell>
+          <cell r="BJ5">
+            <v>902</v>
+          </cell>
+          <cell r="BK5">
+            <v>778</v>
+          </cell>
+          <cell r="BL5">
+            <v>768</v>
+          </cell>
+          <cell r="BM5">
+            <v>837</v>
+          </cell>
+          <cell r="BN5">
+            <v>1006</v>
+          </cell>
+          <cell r="BO5">
+            <v>867</v>
+          </cell>
+          <cell r="BP5">
+            <v>899</v>
+          </cell>
+          <cell r="BQ5">
+            <v>896</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="AW6">
+            <v>600</v>
+          </cell>
+          <cell r="AX6">
+            <v>705</v>
+          </cell>
+          <cell r="AY6">
+            <v>622</v>
+          </cell>
+          <cell r="AZ6">
+            <v>640</v>
+          </cell>
+          <cell r="BA6">
+            <v>636</v>
+          </cell>
+          <cell r="BB6">
+            <v>709</v>
+          </cell>
+          <cell r="BC6">
+            <v>664</v>
+          </cell>
+          <cell r="BD6">
+            <v>666</v>
+          </cell>
+          <cell r="BE6">
+            <v>765</v>
+          </cell>
+          <cell r="BF6">
+            <v>936</v>
+          </cell>
+          <cell r="BG6">
+            <v>778</v>
+          </cell>
+          <cell r="BH6">
+            <v>841</v>
+          </cell>
+          <cell r="BI6">
+            <v>798</v>
+          </cell>
+          <cell r="BJ6">
+            <v>1042</v>
+          </cell>
+          <cell r="BK6">
+            <v>864</v>
+          </cell>
+          <cell r="BL6">
+            <v>908</v>
+          </cell>
+          <cell r="BM6">
+            <v>938</v>
+          </cell>
+          <cell r="BN6">
+            <v>1142</v>
+          </cell>
+          <cell r="BO6">
+            <v>945</v>
+          </cell>
+          <cell r="BP6">
+            <v>990</v>
+          </cell>
+          <cell r="BQ6">
+            <v>985</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="AW7">
+            <v>66</v>
+          </cell>
+          <cell r="AX7">
+            <v>82</v>
+          </cell>
+          <cell r="AY7">
+            <v>289</v>
+          </cell>
+          <cell r="AZ7">
+            <v>301</v>
+          </cell>
+          <cell r="BA7">
+            <v>295</v>
+          </cell>
+          <cell r="BB7">
+            <v>303</v>
+          </cell>
+          <cell r="BC7">
+            <v>301</v>
+          </cell>
+          <cell r="BD7">
+            <v>306</v>
+          </cell>
+          <cell r="BE7">
+            <v>294</v>
+          </cell>
+          <cell r="BF7">
+            <v>299</v>
+          </cell>
+          <cell r="BG7">
+            <v>284</v>
+          </cell>
+          <cell r="BH7">
+            <v>311</v>
+          </cell>
+          <cell r="BI7">
+            <v>311</v>
+          </cell>
+          <cell r="BJ7">
+            <v>320</v>
+          </cell>
+          <cell r="BK7">
+            <v>310</v>
+          </cell>
+          <cell r="BL7">
+            <v>327</v>
+          </cell>
+          <cell r="BM7">
+            <v>329</v>
+          </cell>
+          <cell r="BN7">
+            <v>341</v>
+          </cell>
+          <cell r="BO7">
+            <v>406</v>
+          </cell>
+          <cell r="BP7">
+            <v>498</v>
+          </cell>
+          <cell r="BQ7">
+            <v>525</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="AW8">
+            <v>518</v>
+          </cell>
+          <cell r="AX8">
+            <v>312</v>
+          </cell>
+          <cell r="AY8">
+            <v>281</v>
+          </cell>
+          <cell r="AZ8">
+            <v>310</v>
+          </cell>
+          <cell r="BA8">
+            <v>299</v>
+          </cell>
+          <cell r="BB8">
+            <v>324</v>
+          </cell>
+          <cell r="BC8">
+            <v>323</v>
+          </cell>
+          <cell r="BD8">
+            <v>337</v>
+          </cell>
+          <cell r="BE8">
+            <v>332</v>
+          </cell>
+          <cell r="BF8">
+            <v>384</v>
+          </cell>
+          <cell r="BG8">
+            <v>355</v>
+          </cell>
+          <cell r="BH8">
+            <v>373</v>
+          </cell>
+          <cell r="BI8">
+            <v>384</v>
+          </cell>
+          <cell r="BJ8">
+            <v>764</v>
+          </cell>
+          <cell r="BK8">
+            <v>478</v>
+          </cell>
+          <cell r="BL8">
+            <v>416</v>
+          </cell>
+          <cell r="BM8">
+            <v>441</v>
+          </cell>
+          <cell r="BN8">
+            <v>801</v>
+          </cell>
+          <cell r="BO8">
+            <v>563</v>
+          </cell>
+          <cell r="BP8">
+            <v>616</v>
+          </cell>
+          <cell r="BQ8">
+            <v>637</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="AW10">
+            <v>435</v>
+          </cell>
+          <cell r="AX10">
+            <v>459</v>
+          </cell>
+          <cell r="AY10">
+            <v>412</v>
+          </cell>
+          <cell r="AZ10">
+            <v>474</v>
+          </cell>
+          <cell r="BA10">
+            <v>439</v>
+          </cell>
+          <cell r="BB10">
+            <v>523</v>
+          </cell>
+          <cell r="BC10">
+            <v>464</v>
+          </cell>
+          <cell r="BD10">
+            <v>500</v>
+          </cell>
+          <cell r="BE10">
+            <v>481</v>
+          </cell>
+          <cell r="BF10">
+            <v>552</v>
+          </cell>
+          <cell r="BG10">
+            <v>566</v>
+          </cell>
+          <cell r="BH10">
+            <v>562</v>
+          </cell>
+          <cell r="BI10">
+            <v>515</v>
+          </cell>
+          <cell r="BJ10">
+            <v>630</v>
+          </cell>
+          <cell r="BK10">
+            <v>588</v>
+          </cell>
+          <cell r="BL10">
+            <v>602</v>
+          </cell>
+          <cell r="BM10">
+            <v>570</v>
+          </cell>
+          <cell r="BN10">
+            <v>687</v>
+          </cell>
+          <cell r="BO10">
+            <v>639</v>
+          </cell>
+          <cell r="BP10">
+            <v>640</v>
+          </cell>
+          <cell r="BQ10">
+            <v>628</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="AW11">
+            <v>334</v>
+          </cell>
+          <cell r="AX11">
+            <v>340</v>
+          </cell>
+          <cell r="AY11">
+            <v>309</v>
+          </cell>
+          <cell r="AZ11">
+            <v>353</v>
+          </cell>
+          <cell r="BA11">
+            <v>328</v>
+          </cell>
+          <cell r="BB11">
+            <v>352</v>
+          </cell>
+          <cell r="BC11">
+            <v>327</v>
+          </cell>
+          <cell r="BD11">
+            <v>364</v>
+          </cell>
+          <cell r="BE11">
+            <v>347</v>
+          </cell>
+          <cell r="BF11">
+            <v>375</v>
+          </cell>
+          <cell r="BG11">
+            <v>375</v>
+          </cell>
+          <cell r="BH11">
+            <v>393</v>
+          </cell>
+          <cell r="BI11">
+            <v>362</v>
+          </cell>
+          <cell r="BJ11">
+            <v>414</v>
+          </cell>
+          <cell r="BK11">
+            <v>393</v>
+          </cell>
+          <cell r="BL11">
+            <v>428</v>
+          </cell>
+          <cell r="BM11">
+            <v>420</v>
+          </cell>
+          <cell r="BN11">
+            <v>463</v>
+          </cell>
+          <cell r="BO11">
+            <v>443</v>
+          </cell>
+          <cell r="BP11">
+            <v>466</v>
+          </cell>
+          <cell r="BQ11">
+            <v>457</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="AW12">
+            <v>430</v>
+          </cell>
+          <cell r="AX12">
+            <v>570</v>
+          </cell>
+          <cell r="AY12">
+            <v>640</v>
+          </cell>
+          <cell r="AZ12">
+            <v>674</v>
+          </cell>
+          <cell r="BA12">
+            <v>639</v>
+          </cell>
+          <cell r="BB12">
+            <v>711</v>
+          </cell>
+          <cell r="BC12">
+            <v>685</v>
+          </cell>
+          <cell r="BD12">
+            <v>676</v>
+          </cell>
+          <cell r="BE12">
+            <v>672</v>
+          </cell>
+          <cell r="BF12">
+            <v>774</v>
+          </cell>
+          <cell r="BG12">
+            <v>769</v>
+          </cell>
+          <cell r="BH12">
+            <v>766</v>
+          </cell>
+          <cell r="BI12">
+            <v>752</v>
+          </cell>
+          <cell r="BJ12">
+            <v>860</v>
+          </cell>
+          <cell r="BK12">
+            <v>830</v>
+          </cell>
+          <cell r="BL12">
+            <v>832</v>
+          </cell>
+          <cell r="BM12">
+            <v>849</v>
+          </cell>
+          <cell r="BN12">
+            <v>996</v>
+          </cell>
+          <cell r="BO12">
+            <v>945</v>
+          </cell>
+          <cell r="BP12">
+            <v>957</v>
+          </cell>
+          <cell r="BQ12">
+            <v>960</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="AW13">
+            <v>302</v>
+          </cell>
+          <cell r="AX13">
+            <v>307</v>
+          </cell>
+          <cell r="AY13">
+            <v>278</v>
+          </cell>
+          <cell r="AZ13">
+            <v>307</v>
+          </cell>
+          <cell r="BA13">
+            <v>282</v>
+          </cell>
+          <cell r="BB13">
+            <v>300</v>
+          </cell>
+          <cell r="BC13">
+            <v>279</v>
+          </cell>
+          <cell r="BD13">
+            <v>290</v>
+          </cell>
+          <cell r="BE13">
+            <v>280</v>
+          </cell>
+          <cell r="BF13">
+            <v>297</v>
+          </cell>
+          <cell r="BG13">
+            <v>284</v>
+          </cell>
+          <cell r="BH13">
+            <v>296</v>
+          </cell>
+          <cell r="BI13">
+            <v>291</v>
+          </cell>
+          <cell r="BJ13">
+            <v>122</v>
+          </cell>
+          <cell r="BK13">
+            <v>171</v>
+          </cell>
+          <cell r="BL13">
+            <v>307</v>
+          </cell>
+          <cell r="BM13">
+            <v>304</v>
+          </cell>
+          <cell r="BN13">
+            <v>85</v>
+          </cell>
+          <cell r="BO13">
+            <v>166</v>
+          </cell>
+          <cell r="BP13">
+            <v>5</v>
+          </cell>
+          <cell r="BQ13">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="AW14">
+            <v>118</v>
+          </cell>
+          <cell r="AX14">
+            <v>157</v>
+          </cell>
+          <cell r="AY14">
+            <v>123</v>
+          </cell>
+          <cell r="AZ14">
+            <v>127</v>
+          </cell>
+          <cell r="BA14">
+            <v>123</v>
+          </cell>
+          <cell r="BB14">
+            <v>176</v>
+          </cell>
+          <cell r="BC14">
+            <v>97</v>
+          </cell>
+          <cell r="BD14">
+            <v>114</v>
+          </cell>
+          <cell r="BE14">
+            <v>111</v>
+          </cell>
+          <cell r="BF14">
+            <v>153</v>
+          </cell>
+          <cell r="BG14">
+            <v>94</v>
+          </cell>
+          <cell r="BH14">
+            <v>119</v>
+          </cell>
+          <cell r="BI14">
+            <v>130</v>
+          </cell>
+          <cell r="BJ14">
+            <v>35</v>
+          </cell>
+          <cell r="BK14">
+            <v>164</v>
+          </cell>
+          <cell r="BL14">
+            <v>136</v>
+          </cell>
+          <cell r="BM14">
+            <v>127</v>
+          </cell>
+          <cell r="BN14">
+            <v>125</v>
+          </cell>
+          <cell r="BO14">
+            <v>162</v>
+          </cell>
+          <cell r="BP14">
+            <v>183</v>
+          </cell>
+          <cell r="BQ14">
+            <v>203</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="AW44">
+            <v>4.1817674937273397E-2</v>
+          </cell>
+          <cell r="AX44">
+            <v>3.1711450012103626E-2</v>
+          </cell>
+          <cell r="AY44">
+            <v>0.1017279821627648</v>
+          </cell>
+          <cell r="AZ44">
+            <v>0.55354558610709126</v>
+          </cell>
+          <cell r="BA44">
+            <v>0.11319240032111311</v>
+          </cell>
+          <cell r="BB44">
+            <v>0.10300328484279686</v>
+          </cell>
+          <cell r="BC44">
+            <v>8.1457121173792002E-2</v>
+          </cell>
+          <cell r="BD44">
+            <v>4.6343735444806633E-2</v>
+          </cell>
+          <cell r="BE44">
+            <v>7.6682692307692202E-2</v>
+          </cell>
+          <cell r="BF44">
+            <v>0.10657306955966805</v>
+          </cell>
+          <cell r="BG44">
+            <v>0.11766081871345024</v>
+          </cell>
+          <cell r="BH44">
+            <v>0.11195192521700426</v>
+          </cell>
+          <cell r="BI44">
+            <v>9.6003572225943357E-2</v>
+          </cell>
+          <cell r="BJ44">
+            <v>0.1178392925797771</v>
+          </cell>
+          <cell r="BK44">
+            <v>9.7321054834658804E-2</v>
+          </cell>
+          <cell r="BL44">
+            <v>8.526821457165723E-2</v>
+          </cell>
+          <cell r="BM44">
+            <v>0.11916887349765726</v>
+          </cell>
+          <cell r="BN44">
+            <v>0.10679277730008607</v>
+          </cell>
+          <cell r="BO44">
+            <v>0.11882510013351144</v>
+          </cell>
+          <cell r="BP44">
+            <v>0.11066027296200653</v>
+          </cell>
+          <cell r="BQ44">
+            <v>0.10247542773935203</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="AW55">
+            <v>780</v>
+          </cell>
+          <cell r="AX55">
+            <v>671</v>
+          </cell>
+          <cell r="AY55">
+            <v>367</v>
+          </cell>
+          <cell r="AZ55">
+            <v>662</v>
+          </cell>
+          <cell r="BA55">
+            <v>495</v>
+          </cell>
+          <cell r="BB55">
+            <v>757</v>
+          </cell>
+          <cell r="BC55">
+            <v>386</v>
+          </cell>
+          <cell r="BD55">
+            <v>720</v>
+          </cell>
+          <cell r="BE55">
+            <v>816</v>
+          </cell>
+          <cell r="BF55">
+            <v>761</v>
+          </cell>
+          <cell r="BG55">
+            <v>679</v>
+          </cell>
+          <cell r="BH55">
+            <v>899</v>
+          </cell>
+          <cell r="BI55">
+            <v>869</v>
+          </cell>
+          <cell r="BJ55">
+            <v>1226</v>
+          </cell>
+          <cell r="BK55">
+            <v>923</v>
+          </cell>
+          <cell r="BL55">
+            <v>998</v>
+          </cell>
+          <cell r="BM55">
+            <v>1043</v>
+          </cell>
+          <cell r="BN55">
+            <v>528</v>
+          </cell>
+          <cell r="BO55">
+            <v>764</v>
+          </cell>
+          <cell r="BP55">
+            <v>1016</v>
+          </cell>
+          <cell r="BQ55">
+            <v>1029</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="AW103">
+            <v>829</v>
+          </cell>
+          <cell r="AX103">
+            <v>1237</v>
+          </cell>
+          <cell r="AY103">
+            <v>452</v>
+          </cell>
+          <cell r="AZ103">
+            <v>878</v>
+          </cell>
+          <cell r="BA103">
+            <v>933</v>
+          </cell>
+          <cell r="BB103">
+            <v>1000</v>
+          </cell>
+          <cell r="BC103">
+            <v>203</v>
+          </cell>
+          <cell r="BD103">
+            <v>529</v>
+          </cell>
+          <cell r="BE103">
+            <v>889</v>
+          </cell>
+          <cell r="BF103">
+            <v>1003</v>
+          </cell>
+          <cell r="BG103">
+            <v>445</v>
+          </cell>
+          <cell r="BH103">
+            <v>688</v>
+          </cell>
+          <cell r="BI103">
+            <v>1050</v>
+          </cell>
+          <cell r="BJ103">
+            <v>1528</v>
+          </cell>
+          <cell r="BK103">
+            <v>204</v>
+          </cell>
+          <cell r="BL103">
+            <v>633</v>
+          </cell>
+          <cell r="BM103">
+            <v>1474</v>
+          </cell>
+          <cell r="BN103">
+            <v>1931</v>
+          </cell>
+          <cell r="BO103">
+            <v>250</v>
+          </cell>
+          <cell r="BP103">
+            <v>1111</v>
+          </cell>
+          <cell r="BQ103">
+            <v>1790</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="188">
+          <cell r="J188" t="str">
+            <v>[X]</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="J189" t="str">
+            <v>[Y]</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="J190" t="str">
+            <v>[Z]</v>
+          </cell>
+        </row>
+        <row r="224">
+          <cell r="J224" t="str">
+            <v>[X]</v>
+          </cell>
+        </row>
+        <row r="225">
+          <cell r="J225" t="str">
+            <v>[Y]</v>
+          </cell>
+        </row>
+        <row r="226">
+          <cell r="J226" t="str">
+            <v>[Z]</v>
+          </cell>
+        </row>
+        <row r="258">
+          <cell r="J258" t="str">
+            <v xml:space="preserve">The return distribution fits a Gaussian curve well, implying that daily change follows a roughly normal distribution </v>
+          </cell>
+        </row>
+        <row r="259">
+          <cell r="J259" t="str">
+            <v xml:space="preserve">There is slight implied upside to mean 1-day returns </v>
+          </cell>
+        </row>
+        <row r="261">
+          <cell r="J261" t="str">
+            <v>Min</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="J262" t="str">
+            <v>Max</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main | Overview"/>
+      <sheetName val="Model"/>
+      <sheetName val="Notes | Quant Analysis"/>
+      <sheetName val="M&amp;A Scope"/>
+      <sheetName val="Markets | Product Lines"/>
+      <sheetName val="Management"/>
+      <sheetName val="Debt Schedule"/>
+      <sheetName val="Clinical Trial Channel"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="AW3" t="str">
+            <v>Q1 2020</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
